--- a/reports/latest/Test_Report_BurnoutTracker.xlsx
+++ b/reports/latest/Test_Report_BurnoutTracker.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BurnOutTracker Web App - Selenium E2E Workflow</t>
+          <t>BurnOutTracker Android App - Full Appium E2E Workflow</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -489,16 +489,16 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-30T13:26:09.233049Z</t>
+          <t>2026-07-30T13:47:30.748392Z</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-30T13:26:19.011872Z</t>
+          <t>2026-07-30T13:49:02.595600Z</t>
         </is>
       </c>
     </row>
